--- a/july 2026/LMT_JULY_26/Decent Johar Town.xlsx
+++ b/july 2026/LMT_JULY_26/Decent Johar Town.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B925CD-D5EA-41E7-B758-62972D4990CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1AD99BD-84D7-4CEB-9DB8-307F93DC99C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3223,7 +3223,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -3251,7 +3251,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -4444,7 +4444,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -4472,7 +4472,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -5665,7 +5665,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -5693,7 +5693,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -6886,7 +6886,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -6914,7 +6914,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -8107,7 +8107,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -8135,7 +8135,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -9328,7 +9328,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -9356,7 +9356,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -10546,7 +10546,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -10574,7 +10574,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -11763,7 +11763,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -11791,7 +11791,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -12980,7 +12980,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -13008,7 +13008,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -14197,7 +14197,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -14225,7 +14225,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -18164,7 +18164,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -18192,7 +18192,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -19381,7 +19381,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -19409,7 +19409,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -20598,7 +20598,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -20626,7 +20626,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -21815,7 +21815,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -21843,7 +21843,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -23037,7 +23037,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -23065,7 +23065,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -24622,7 +24622,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -24650,7 +24650,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -26128,7 +26128,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -26156,7 +26156,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -27349,7 +27349,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -27377,7 +27377,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -28569,7 +28569,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -28597,7 +28597,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -29790,7 +29790,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -29818,7 +29818,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -31011,7 +31011,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -31039,7 +31039,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
